--- a/data/helper/Lemond Size Chart.xlsx
+++ b/data/helper/Lemond Size Chart.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/Sizing/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/helper/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6AC295B-BD47-8E45-B82E-6CF59F0BE691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D4A772B-EB83-7648-BC47-ED7433DA9792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31900" yWindow="-23400" windowWidth="27640" windowHeight="16440" xr2:uid="{C2C59952-402B-6149-A87A-5787A23567B7}"/>
+    <workbookView xWindow="33120" yWindow="-22780" windowWidth="27640" windowHeight="16440" xr2:uid="{C2C59952-402B-6149-A87A-5787A23567B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <r>
       <t>Here’s the transcription of </t>
@@ -88,10 +88,16 @@
     <t>intercept</t>
   </si>
   <si>
-    <t>height</t>
+    <t>inseam</t>
   </si>
   <si>
-    <t>inseam</t>
+    <t>x</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>frame size</t>
   </si>
 </sst>
 </file>
@@ -488,18 +494,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE71F51C-FD08-7C4F-AF2D-F316C70D6EDC}">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="6" width="19.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -518,8 +533,16 @@
       <c r="F3" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>26</v>
       </c>
@@ -542,11 +565,11 @@
         <v>7</v>
       </c>
       <c r="H4">
-        <f>SLOPE(B4:B39,F4:F39)</f>
-        <v>1.132404245387318</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+        <f>SLOPE(B4:B39,D4:D39)</f>
+        <v>1.5423279404570587</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>26.5</v>
       </c>
@@ -569,11 +592,11 @@
         <v>8</v>
       </c>
       <c r="H5">
-        <f>INTERCEPT(B4:B39,F4:F39)</f>
-        <v>1.4629142815010709E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+        <f>INTERCEPT(B4:B39,D4:D39)</f>
+        <v>-0.24153589417326771</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>27</v>
       </c>
@@ -592,14 +615,8 @@
       <c r="F6">
         <v>60.6</v>
       </c>
-      <c r="G6" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>27.5</v>
       </c>
@@ -623,10 +640,10 @@
       </c>
       <c r="H7">
         <f>H5+H4*G7</f>
-        <v>77.471079527307566</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+        <v>105.25369523308956</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>28</v>
       </c>
@@ -646,7 +663,7 @@
         <v>62.8</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>28.5</v>
       </c>
@@ -666,7 +683,7 @@
         <v>63.9</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>29</v>
       </c>
@@ -686,7 +703,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>29.5</v>
       </c>
@@ -706,7 +723,7 @@
         <v>66.2</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>30</v>
       </c>
@@ -726,7 +743,7 @@
         <v>67.3</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>30.5</v>
       </c>
@@ -746,7 +763,7 @@
         <v>68.400000000000006</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>31</v>
       </c>
@@ -766,7 +783,7 @@
         <v>69.5</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>31.5</v>
       </c>
@@ -786,7 +803,7 @@
         <v>70.599999999999994</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>32</v>
       </c>
